--- a/Assets/Plugins/ExcelTool/灭鼠喷雾.xlsx
+++ b/Assets/Plugins/ExcelTool/灭鼠喷雾.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="14175" firstSheet="2" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="14175" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="玩家数据" sheetId="1" r:id="rId1"/>
@@ -56,10 +56,13 @@
           <t xml:space="preserve">
     None,
     First = 1,//首次引导结束后
-    Item = 2,//物品持有
-    ItemProduce = 3,//物品产出
+    Mouse= 2,//消灭老鼠
+    Transport= 3,//搬运病人
     UnlockIcon = 4,//解锁图标
-    UnlockFinish = 5,//解锁完成</t>
+    UnlockFinish = 5,//解锁完成
+    Treatment=6,//治疗病人
+    PatientMoney=7,//病人留下金币
+    Money=8,//鸟嘴金币数量达到x</t>
         </r>
       </text>
     </comment>
@@ -71,13 +74,16 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">类型备注(同触发):
+          <t xml:space="preserve">类型备注:
     None,
     First = 1,//首次引导结束后
-    Item = 2,//物品持有
-    ItemProduce = 3,//物品产出
+    Mouse= 2,//消灭老鼠
+    Transport= 3,//搬运病人
     UnlockIcon = 4,//解锁图标
     UnlockFinish = 5,//解锁完成
+    Treatment=6,//治疗病人
+    PatientMoney=7,//病人留下金币
+    Money=8,//鸟嘴金币数量达到x
 </t>
         </r>
       </text>
@@ -87,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="109">
   <si>
     <t>参数表</t>
   </si>
@@ -149,10 +155,13 @@
     <t>enemyKnockbackForc</t>
   </si>
   <si>
+    <t>1颗金币=10块钱</t>
+  </si>
+  <si>
     <t>老鼠掉落金币值</t>
   </si>
   <si>
-    <t>enemyDropNum</t>
+    <t>enemyDropMoney</t>
   </si>
   <si>
     <t>初始老鼠数量</t>
@@ -221,7 +230,7 @@
     <t>场景升级</t>
   </si>
   <si>
-    <t>其他通用配置</t>
+    <t>通用参数</t>
   </si>
   <si>
     <t>小麦生长时间</t>
@@ -230,12 +239,6 @@
     <t>wheatTime</t>
   </si>
   <si>
-    <t>传送带速度</t>
-  </si>
-  <si>
-    <t>conveyorTime</t>
-  </si>
-  <si>
     <t>门口普通病人上限</t>
   </si>
   <si>
@@ -245,7 +248,7 @@
     <t>门口泡汤类病人上限</t>
   </si>
   <si>
-    <t>famerPatientNum</t>
+    <t>farmerPatientNum</t>
   </si>
   <si>
     <t>电梯升/降时间</t>
@@ -254,22 +257,100 @@
     <t>elevatorTime</t>
   </si>
   <si>
-    <t>治愈泡汤病人需要小麦数量</t>
+    <t>病人打针后掉落金币值</t>
+  </si>
+  <si>
+    <t>patienMoney</t>
+  </si>
+  <si>
+    <t>病人泡汤后掉落金币值</t>
+  </si>
+  <si>
+    <t>farmerPatienMoney</t>
+  </si>
+  <si>
+    <t>病人泡汤消耗小麦数量</t>
   </si>
   <si>
     <t>wheatPerPatient</t>
   </si>
   <si>
-    <t>普通病人掉落金币值</t>
-  </si>
-  <si>
-    <t>patienMoney</t>
-  </si>
-  <si>
-    <t>泡汤病人掉落金币值</t>
-  </si>
-  <si>
-    <t>famerPatienMoney</t>
+    <t>打针给金币的金币储存上限</t>
+  </si>
+  <si>
+    <t>maxPatient1</t>
+  </si>
+  <si>
+    <t>泡汤给金币的金币储存上限</t>
+  </si>
+  <si>
+    <t>maxPatient2</t>
+  </si>
+  <si>
+    <t>战士金币存储最大高度</t>
+  </si>
+  <si>
+    <t>maxPatient3</t>
+  </si>
+  <si>
+    <t>一颗金币价值</t>
+  </si>
+  <si>
+    <t>moneyValue</t>
+  </si>
+  <si>
+    <t>效率参数</t>
+  </si>
+  <si>
+    <t>每个npc采集麦子的效率_间隔(秒)</t>
+  </si>
+  <si>
+    <t>collectTime</t>
+  </si>
+  <si>
+    <t>每个npc采集麦子的效率_数量</t>
+  </si>
+  <si>
+    <t>collectNum</t>
+  </si>
+  <si>
+    <t>战士的掉血效率_间隔(秒)</t>
+  </si>
+  <si>
+    <t>HpTime</t>
+  </si>
+  <si>
+    <t>战士的掉血效率_百分比</t>
+  </si>
+  <si>
+    <t>HpPecent</t>
+  </si>
+  <si>
+    <t>其他参数</t>
+  </si>
+  <si>
+    <t>主角一次运送普通病人的数量上限</t>
+  </si>
+  <si>
+    <t>maxPatienNum</t>
+  </si>
+  <si>
+    <t>主角一次运送泡汤病人的数量上限</t>
+  </si>
+  <si>
+    <t>maxfarmerPatienNum</t>
+  </si>
+  <si>
+    <t>泡汤区一次最多容纳的病人数量上限</t>
+  </si>
+  <si>
+    <t>maxSoakNum</t>
+  </si>
+  <si>
+    <t>电梯最大容纳农夫数量</t>
+  </si>
+  <si>
+    <t>maxElevatorNum</t>
   </si>
   <si>
     <t>引导列表说明</t>
@@ -320,22 +401,25 @@
     <t>hideName</t>
   </si>
   <si>
+    <t>Clerk_护士</t>
+  </si>
+  <si>
     <t>引导根据triggerType的类型与数量触发</t>
   </si>
   <si>
-    <t>triggerName为触发绑定的细分类型：如肉片</t>
-  </si>
-  <si>
-    <t>根据hideType的类型与数量判定完成</t>
-  </si>
-  <si>
-    <t>hideName为完成绑定的细分类型：如肉片</t>
-  </si>
-  <si>
-    <t>以id=2为例：当大肉块产出数量&gt;=10，则触发该引导</t>
-  </si>
-  <si>
-    <t>当大肉块持有数量&gt;=1，则移除该引导</t>
+    <t>Clerk_搬运工</t>
+  </si>
+  <si>
+    <t>triggerName为触发绑定的细分类型</t>
+  </si>
+  <si>
+    <t>Clerk_泡汤池</t>
+  </si>
+  <si>
+    <t>Clerk_大场景</t>
+  </si>
+  <si>
+    <t>消灭老鼠引导</t>
   </si>
 </sst>
 </file>
@@ -348,8 +432,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -836,152 +928,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1009,10 +1101,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1577,10 +1684,10 @@
       </c>
     </row>
     <row r="3" spans="2:5">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="8">
@@ -1740,14 +1847,14 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D3" s="8">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1785,14 +1892,17 @@
       </c>
     </row>
     <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>12</v>
@@ -1800,10 +1910,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="B7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" s="8">
         <v>5</v>
@@ -1915,7 +2025,7 @@
   <sheetData>
     <row r="1" customFormat="1" spans="1:7">
       <c r="B1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s">
         <v>12</v>
@@ -1924,64 +2034,61 @@
         <v>12</v>
       </c>
       <c r="E1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" t="s">
         <v>12</v>
       </c>
       <c r="G1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" customFormat="1" spans="1:7">
       <c r="B3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="10" t="s">
         <v>37</v>
       </c>
+      <c r="E3" s="14" t="s">
+        <v>38</v>
+      </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1989,23 +2096,19 @@
       <c r="D4">
         <v>50</v>
       </c>
-      <c r="E4" s="10"/>
+      <c r="E4" s="14"/>
       <c r="F4">
         <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
-      <c r="D5"/>
-      <c r="E5" s="10">
+      <c r="E5" s="14">
         <v>1</v>
       </c>
       <c r="F5">
@@ -2014,41 +2117,35 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
-      <c r="D6"/>
-      <c r="E6" s="10">
+      <c r="E6" s="14">
         <v>2</v>
       </c>
       <c r="F6">
-        <v>200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:7">
       <c r="A7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B7"/>
       <c r="C7">
         <v>4</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="14">
         <v>3</v>
       </c>
       <c r="F7">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:7">
-      <c r="E8" s="10"/>
+      <c r="E8" s="14"/>
     </row>
     <row r="9" customFormat="1" spans="1:7">
       <c r="E9" s="8"/>
@@ -2135,7 +2232,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="34.8571428571429" customWidth="1"/>
-    <col min="2" max="2" width="25.4285714285714" customWidth="1"/>
+    <col min="2" max="2" width="30.4285714285714" customWidth="1"/>
     <col min="3" max="3" width="24.7142857142857" customWidth="1"/>
     <col min="4" max="4" width="25.4285714285714" customWidth="1"/>
   </cols>
@@ -2159,46 +2256,46 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" customFormat="1" spans="1:5">
-      <c r="A3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="9" t="s">
+    <row r="3" s="9" customFormat="1" spans="1:5">
+      <c r="A3" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="8">
+      <c r="C3" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="12">
         <v>3</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" customFormat="1" spans="1:5">
       <c r="B4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4" s="8">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:5">
       <c r="B5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D5" s="8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -2206,41 +2303,41 @@
     </row>
     <row r="6" customFormat="1" spans="1:5">
       <c r="B6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6" s="8">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:5">
       <c r="B7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D7" s="8">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:5">
       <c r="B8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D8" s="8">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
@@ -2248,13 +2345,13 @@
     </row>
     <row r="9" customFormat="1" spans="1:5">
       <c r="B9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D9" s="8">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
@@ -2262,82 +2359,209 @@
     </row>
     <row r="10" customFormat="1" spans="1:5">
       <c r="B10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D10" s="8">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:5">
-      <c r="D11" s="8"/>
+      <c r="B11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="8">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="12" customFormat="1" spans="1:5">
-      <c r="D12" s="8"/>
+      <c r="B12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="8">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="13" customFormat="1" spans="1:5">
-      <c r="D13" s="8"/>
-    </row>
-    <row r="14" customFormat="1" spans="1:5">
-      <c r="D14" s="8"/>
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="8">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" s="9" customFormat="1" spans="1:5">
+      <c r="A14" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="12">
+        <v>2</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="15" customFormat="1" spans="1:5">
-      <c r="D15" s="8"/>
+      <c r="B15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="8">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="16" customFormat="1" spans="1:5">
-      <c r="D16" s="8"/>
-    </row>
-    <row r="17" customFormat="1" spans="4:4">
-      <c r="D17" s="8"/>
-    </row>
-    <row r="18" customFormat="1" spans="4:4">
-      <c r="D18" s="8"/>
-    </row>
-    <row r="19" customFormat="1" spans="4:4">
-      <c r="D19" s="8"/>
-    </row>
-    <row r="20" customFormat="1" spans="4:4">
-      <c r="D20" s="8"/>
-    </row>
-    <row r="21" customFormat="1" spans="4:4">
-      <c r="D21" s="8"/>
-    </row>
-    <row r="22" customFormat="1" spans="4:4">
+      <c r="B16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="8">
+        <v>2</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" spans="1:5">
+      <c r="B17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="8">
+        <v>5</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" s="9" customFormat="1" spans="1:5">
+      <c r="A18" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="12">
+        <v>6</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="1:5">
+      <c r="B19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="8">
+        <v>3</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" spans="1:5">
+      <c r="B20" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="8">
+        <v>3</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" spans="1:5">
+      <c r="B21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" t="s">
+        <v>85</v>
+      </c>
+      <c r="D21" s="8">
+        <v>6</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="1:5">
       <c r="D22" s="8"/>
     </row>
-    <row r="23" customFormat="1" spans="4:4">
+    <row r="23" customFormat="1" spans="1:5">
       <c r="D23" s="8"/>
     </row>
-    <row r="24" customFormat="1" spans="4:4">
+    <row r="24" customFormat="1" spans="1:5">
       <c r="D24" s="8"/>
     </row>
-    <row r="25" customFormat="1" spans="4:4">
+    <row r="25" customFormat="1" spans="1:5">
       <c r="D25" s="8"/>
     </row>
-    <row r="26" customFormat="1" spans="4:4">
+    <row r="26" customFormat="1" spans="1:5">
       <c r="D26" s="8"/>
     </row>
-    <row r="27" customFormat="1" spans="4:4">
+    <row r="27" customFormat="1" spans="1:5">
       <c r="D27" s="8"/>
     </row>
-    <row r="28" customFormat="1" spans="4:4">
+    <row r="28" customFormat="1" spans="1:5">
       <c r="D28" s="8"/>
     </row>
-    <row r="29" customFormat="1" spans="4:4">
+    <row r="29" customFormat="1" spans="1:5">
       <c r="D29" s="8"/>
     </row>
-    <row r="30" customFormat="1" spans="4:4">
+    <row r="30" customFormat="1" spans="1:5">
       <c r="D30" s="8"/>
     </row>
-    <row r="31" customFormat="1" spans="4:4">
+    <row r="31" customFormat="1" spans="1:5">
       <c r="D31" s="8"/>
     </row>
-    <row r="32" customFormat="1" spans="4:4">
+    <row r="32" customFormat="1" spans="1:5">
       <c r="D32" s="8"/>
     </row>
     <row r="33" customFormat="1" spans="4:4">
@@ -2355,7 +2579,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="45.5714285714286" customWidth="1"/>
@@ -2370,7 +2594,7 @@
   <sheetData>
     <row r="1" customFormat="1" spans="1:10">
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>12</v>
@@ -2385,7 +2609,7 @@
         <v>12</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -2394,180 +2618,173 @@
         <v>12</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" customFormat="1" spans="1:10">
       <c r="B2" s="1" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" customFormat="1" spans="1:10">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" customFormat="1" spans="1:10">
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
+      <c r="B4" s="1"/>
       <c r="C4" s="1">
         <v>1</v>
       </c>
       <c r="D4" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="5">
-        <v>1</v>
-      </c>
-      <c r="F4" s="5">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5" t="s">
+        <v>102</v>
+      </c>
       <c r="H4" s="3">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6">
-        <v>0</v>
-      </c>
-      <c r="J4" s="6"/>
+        <v>5</v>
+      </c>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="5" customFormat="1" spans="1:10">
       <c r="A5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="B5" s="1"/>
       <c r="C5" s="1">
         <v>2</v>
       </c>
       <c r="D5" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="5">
-        <v>3</v>
-      </c>
-      <c r="F5" s="5">
-        <v>10</v>
-      </c>
-      <c r="G5" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5" t="s">
+        <v>104</v>
+      </c>
       <c r="H5" s="3">
-        <v>2</v>
-      </c>
-      <c r="I5" s="6">
-        <v>1</v>
-      </c>
-      <c r="J5" s="6"/>
+        <v>5</v>
+      </c>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="6" customFormat="1" spans="1:10">
       <c r="A6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" s="1">
-        <v>3</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="B6" s="1"/>
       <c r="C6" s="1">
         <v>3</v>
       </c>
       <c r="D6" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5">
-        <v>1</v>
-      </c>
-      <c r="F6" s="5">
-        <v>10</v>
-      </c>
-      <c r="G6" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5" t="s">
+        <v>106</v>
+      </c>
       <c r="H6" s="3">
-        <v>3</v>
-      </c>
-      <c r="I6" s="6">
-        <v>1</v>
-      </c>
-      <c r="J6" s="6"/>
+        <v>5</v>
+      </c>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="7" customFormat="1" spans="1:10">
-      <c r="B7" s="1">
-        <v>4</v>
-      </c>
+      <c r="B7" s="1"/>
       <c r="C7" s="1">
         <v>4</v>
       </c>
       <c r="D7" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5">
-        <v>3</v>
-      </c>
-      <c r="F7" s="5">
-        <v>10</v>
-      </c>
-      <c r="G7" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="H7" s="3">
-        <v>2</v>
-      </c>
-      <c r="I7" s="6">
-        <v>1</v>
-      </c>
-      <c r="J7" s="6"/>
+        <v>5</v>
+      </c>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="8" customFormat="1" spans="1:10">
-      <c r="B8" s="1">
-        <v>5</v>
-      </c>
+      <c r="A8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="1"/>
       <c r="C8" s="1">
         <v>5</v>
       </c>
@@ -2577,78 +2794,58 @@
       <c r="E8" s="5">
         <v>1</v>
       </c>
-      <c r="F8" s="5">
-        <v>10</v>
-      </c>
+      <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="3">
-        <v>3</v>
-      </c>
-      <c r="I8" s="6">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I8" s="6"/>
       <c r="J8" s="6"/>
     </row>
     <row r="9" customFormat="1" spans="1:10">
-      <c r="A9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" s="1">
-        <v>6</v>
-      </c>
+      <c r="B9" s="1"/>
       <c r="C9" s="1">
         <v>6</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="8">
         <v>1</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="2">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="3">
         <v>3</v>
       </c>
-      <c r="F9" s="5">
-        <v>10</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="3">
-        <v>2</v>
-      </c>
-      <c r="I9" s="6">
+      <c r="I9" s="3">
         <v>1</v>
       </c>
-      <c r="J9" s="6"/>
+      <c r="J9" s="3"/>
     </row>
     <row r="10" customFormat="1" spans="1:10">
-      <c r="A10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" s="1">
-        <v>7</v>
-      </c>
+      <c r="B10" s="1"/>
       <c r="C10" s="1">
         <v>7</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="8">
         <v>1</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="2">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2">
         <v>1</v>
       </c>
-      <c r="F10" s="5">
-        <v>10</v>
-      </c>
-      <c r="G10" s="5"/>
+      <c r="G10" s="2"/>
       <c r="H10" s="3">
-        <v>3</v>
-      </c>
-      <c r="I10" s="6">
-        <v>1</v>
-      </c>
-      <c r="J10" s="6"/>
+        <v>6</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
     </row>
     <row r="11" customFormat="1" spans="1:10">
-      <c r="B11" s="1">
-        <v>8</v>
-      </c>
+      <c r="B11" s="1"/>
       <c r="C11" s="1">
         <v>8</v>
       </c>
@@ -2656,119 +2853,28 @@
         <v>1</v>
       </c>
       <c r="E11" s="2">
-        <v>3</v>
-      </c>
-      <c r="F11" s="2">
-        <v>10</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="3">
-        <v>2</v>
-      </c>
-      <c r="I11" s="3">
-        <v>1</v>
-      </c>
-      <c r="J11" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="12" customFormat="1" spans="1:10">
-      <c r="A12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B12" s="1">
-        <v>9</v>
-      </c>
-      <c r="C12" s="1">
-        <v>9</v>
-      </c>
-      <c r="D12" s="8">
-        <v>1</v>
-      </c>
-      <c r="E12" s="2">
-        <v>4</v>
-      </c>
-      <c r="F12" s="2">
-        <v>1</v>
-      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="3">
-        <v>5</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1</v>
-      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
       <c r="J12" s="3"/>
-    </row>
-    <row r="13" customFormat="1" spans="1:10">
-      <c r="A13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B13" s="1">
-        <v>10</v>
-      </c>
-      <c r="C13" s="1">
-        <v>10</v>
-      </c>
-      <c r="D13" s="8">
-        <v>1</v>
-      </c>
-      <c r="E13" s="2">
-        <v>4</v>
-      </c>
-      <c r="F13" s="2">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="3">
-        <v>5</v>
-      </c>
-      <c r="I13" s="3">
-        <v>1</v>
-      </c>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" customFormat="1" spans="1:10">
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-    </row>
-    <row r="15" customFormat="1" spans="1:10">
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16" customFormat="1" spans="1:10">
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-    </row>
-    <row r="17" customFormat="1" spans="2:10">
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
